--- a/artfynd/A 26399-2026 artfynd.xlsx
+++ b/artfynd/A 26399-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,50 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124034849</v>
+        <v>75574223</v>
       </c>
       <c r="B2" t="n">
-        <v>91023</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91458</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1205</v>
+        <v>936</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Stor aspticka</t>
+          <t>Spinnfingersvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinus populicola</t>
+          <t>Lentaria byssiseda</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Pers.) Corner</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Tvärena, Tvärena, Upl</t>
+          <t>Björinge 4 km SV om Edebo kyrka, Upl</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>696652</v>
+        <v>696410</v>
       </c>
       <c r="R2" t="n">
-        <v>6654409</v>
+        <v>6654439</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,12 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>1997-09-17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-04-13</t>
+          <t>1997-09-17</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>På mossbevuxen stam av levande ek, omkr. 84 cm.</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -762,18 +762,259 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>Skogsek</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Mossbevuxen stam av levande ek. # Skogsek</t>
+        </is>
+      </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>Gillis Aronsson</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>124034849</v>
+      </c>
+      <c r="B3" t="n">
+        <v>91920</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1205</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Stor aspticka</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Phellinus populicola</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tvärena, Tvärena, Upl</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>696652</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6654409</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2025-04-13</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>Liam Sebestyén</t>
         </is>
       </c>
-      <c r="AY2" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>105041247</v>
+      </c>
+      <c r="B4" t="n">
+        <v>43428</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>100943</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Asknätfjäril</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Euphydryas maturna</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>larv/nymf</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björinge, Upl</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>696302</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6654353</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Edebo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2022-09-05</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Mårten Nilsson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 26399-2026 artfynd.xlsx
+++ b/artfynd/A 26399-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AZ4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -784,6 +789,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/75574223</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -881,6 +891,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124034849</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1015,8 +1030,18 @@
           <t>Biogeografisk uppföljning av fjärilar, Asknätfjäril ÅGP</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/105041247</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>